--- a/prep_and_checklists/Holiday Magazine  /PREPLIST_Holiday Magazine  _06-17-2026_0.xlsx
+++ b/prep_and_checklists/Holiday Magazine  /PREPLIST_Holiday Magazine  _06-17-2026_0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/prep_and_checklists/Holiday Magazine  /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87933BF-DE8F-D04E-B1F1-12743AA003B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5660A913-F0E5-2E45-B954-65F8E8565CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1016,6 +1016,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1523,7 +1526,7 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup scale="46" orientation="landscape"/>
 </worksheet>
 </file>
 
@@ -2284,5 +2287,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>